--- a/aq_files/0079.xlsx
+++ b/aq_files/0079.xlsx
@@ -1,98 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="dataset" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>A jar contains 6 red and 4 blue marbles. Two marbles are drawn one after another with replacement. What is the probability that both are red?</t>
-  </si>
-  <si>
-    <t>A bag contains 5 green and 7 yellow balls. Two balls are drawn without replacement. What is the probability that both are yellow?</t>
-  </si>
-  <si>
-    <t>A box has 3 defective and 9 non-defective bulbs. Two bulbs are selected with replacement. Find the probability that both are defective.</t>
-  </si>
-  <si>
-    <t>From a deck of 52 playing cards, two cards are drawn without replacement. What is the probability that both are aces?</t>
-  </si>
-  <si>
-    <t>A bowl contains 8 chocolates and 2 candies. If two items are picked with replacement, what is the probability that both are chocolates?</t>
-  </si>
-  <si>
-    <t>A class has 10 boys and 15 girls. Two students are selected without replacement. What is the probability that both are girls?</t>
-  </si>
-  <si>
-    <t>A box contains 4 white, 5 black, and 1 red ball. Two balls are drawn with replacement. Find the probability of getting one white and one red (in any order).</t>
-  </si>
-  <si>
-    <t>A jar contains 3 blue, 3 green, and 4 yellow marbles. Two marbles are drawn without replacement. What is the probability that both are green?</t>
-  </si>
-  <si>
-    <t>A lottery drum has 20 tickets numbered 1 to 20. Two tickets are drawn with replacement. What is the probability that both are even numbers?</t>
-  </si>
-  <si>
-    <t>A basket contains 6 apples and 4 oranges. Two fruits are picked without replacement. What is the probability that both are apples?</t>
-  </si>
-  <si>
-    <t>A bag has 2 red, 3 blue, and 5 green balls. Two balls are drawn with replacement. What is the probability that both are of the same color?</t>
-  </si>
-  <si>
-    <t>A library shelf has 8 math books and 12 science books. Two books are selected without replacement. What is the probability that both are science books?</t>
-  </si>
-  <si>
-    <t>A jar contains 5 coins of ₹1 and 5 coins of ₹2. Two coins are drawn with replacement. What is the probability that both are ₹2 coins?</t>
-  </si>
-  <si>
-    <t>From a group of 7 men and 3 women, two people are selected without replacement. What is the probability that both are men?</t>
-  </si>
-  <si>
-    <t>A box contains 10 bulbs, 3 of which are defective. Two bulbs are selected with replacement. What is the probability that exactly one is defective?</t>
-  </si>
-  <si>
-    <t>A set of 12 cards numbered 1–12 is given. Two cards are drawn without replacement. What is the probability that both numbers are greater than 6?</t>
-  </si>
-  <si>
-    <t>A jar contains 4 red and 6 blue balls. Two balls are drawn with replacement. What is the probability that at least one is red?</t>
-  </si>
-  <si>
-    <t>A bag contains 9 balls, 4 of which are black. Two balls are drawn without replacement. What is the probability that none are black?</t>
-  </si>
-  <si>
-    <t>A drawer contains 5 pairs of socks (10 individual socks). Two socks are picked with replacement. What is the probability both are from the same pair?</t>
-  </si>
-  <si>
-    <t>A box has 6 pens and 4 pencils. Two items are chosen without replacement. What is the probability that one is a pen and the other is a pencil?</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="10.0"/>
+      <name val="Arial"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Arial"/>
       <color theme="1"/>
-      <name val="Arial"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
@@ -102,29 +39,86 @@
     <border/>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -322,113 +316,1018 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:B31"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Task_ID,Task_Name,RDD_Operation,Operation_Type,PySpark_Code_Snippet,Input_Records,Output_Records,Execution_Time_Sec,Partitions,Data_Size_MB,Shuffle_MB,Memory_MB,Lineage_Length,Success_Status,Use_Case</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>RDD-001,Load_Text_File,textFile,Create,sc.textFile("data.txt"),10000000,10000000,8,4,1024,0,2048,1,Success,Load external data</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>RDD-002,Parallelize_List,parallelize,Create,sc.parallelize([1,2,3,4,5]),100000,100000,2,2,8,0,512,1,Success,Create RDD from list</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>RDD-003,Whole_Text_Files,wholeTextFiles,Create,sc.wholeTextFiles("folder/"),5000,5000,5,8,256,0,1024,1,Success,Load multiple text files</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>RDD-004,Filter_Numbers,filter,Transformation,rdd.filter(lambda x: x &gt; 100),10000000,5000000,12,4,512,0,1024,2,Success,Filter data by condition</t>
+        </is>
+      </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>RDD-005,Map_Values,map,Transformation,rdd.map(lambda x: x * 2),10000000,10000000,15,4,1024,0,1024,2,Success,Apply function to each element</t>
+        </is>
+      </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>RDD-006,FlatMap_Words,flatMap,Transformation,rdd.flatMap(lambda x: x.split()),5000000,15000000,25,12,1536,0,2048,3,Success,Split lines into words</t>
+        </is>
+      </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>RDD-007,Map_Partitions,mapPartitions,Transformation,rdd.mapPartitions(process_partition),10000000,10000000,20,8,1024,0,2048,2,Success,Batch process each partition</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>RDD-008,Reduce_Sum,reduce,Action,rdd.reduce(lambda a,b: a+b),10000000,1,22,4,1024,1280,3072,5,Success,Aggregate all values</t>
+        </is>
+      </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>RDD-009,Collect_Results,collect,Action,rdd.collect(),10000000,10000000,35,4,1024,0,4096,4,Partial,Return all data to driver</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>RDD-010,Take_Sample,take,Action,rdd.take(100),10000000,100,2,4,1024,0,256,3,Success,Get first n elements</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>RDD-011,Count_Elements,count,Action,rdd.count(),10000000,1,8,4,1024,0,512,4,Success,Count total elements</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>RDD-012,Count_By_Value,countByValue,Action,rdd.countByValue(),10000000,500000,12,4,1024,1280,2048,4,Success,Count frequency of values</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>RDD-013,Group_By_Key,groupByKey,Transformation,rdd.groupByKey(),12000000,8000000,45,12,3072,2560,4096,5,Success,Group values by key</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>RDD-014,Reduce_By_Key,reduceByKey,Transformation,rdd.reduceByKey(lambda a,b: a+b),12000000,3000000,28,8,2048,1920,3072,4,Success,Reduce by key with map-side combine</t>
+        </is>
+      </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>MCQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>RDD-015,Sort_By_Key,sortByKey,Transformation,rdd.sortByKey(),18000000,18000000,68,8,3072,3840,4096,6,Success,Sort RDD by keys</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>RDD-016,Join_RDDs,join,Transformation,rdd1.join(rdd2),20000000,15000000,120,16,4096,5120,8192,7,Success,Inner join two RDDs</t>
+        </is>
+      </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>RDD-017,Union_RDDs,union,Transformation,rdd1.union(rdd2),25000000,25000000,18,8,2048,0,3072,3,Success,Combine two RDDs</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>RDD-018,Distinct_Elements,distinct,Transformation,rdd.distinct(),12000000,6000000,42,16,2560,2560,4096,5,Success,Remove duplicates</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>RDD-019,Intersection_RDDs,intersection,Transformation,rdd1.intersection(rdd2),8000000,4000000,35,8,2048,1280,3072,5,Success,Common elements in two RDDs</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>RDD-020,Subtract_RDDs,subtract,Transformation,rdd1.subtract(rdd2),10000000,4000000,28,8,2048,1280,3072,5,Success,Elements in rdd1 not in rdd2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>RDD-021,Coalesce_Partitions,coalesce,Transformation,rdd.coalesce(4),20000000,20000000,12,4,2048,0,2048,3,Success,Reduce partitions without shuffle</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>RDD-022,Repartition,repartition,Transformation,rdd.repartition(16),10000000,10000000,25,16,1024,1280,2048,4,Success,Increase/decrease partitions with shuffle</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>RDD-023,Cache_RDD,cache,Transformation,rdd.cache(),15000000,15000000,5,8,2048,0,4096,4,Success,Store in memory</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>RDD-024,Persist_Memory,persist,Transformation,rdd.persist(StorageLevel.MEMORY_ONLY),20000000,20000000,8,8,3072,0,8192,4,Success,Persist with storage level</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>RDD-025,Unpersist,unpersist,Action,rdd.unpersist(),15000000,15000000,3,8,0,0,1024,5,Success,Remove from memory</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>RDD-026,Checkpoint,checkpoint,Transformation,rdd.checkpoint(),25000000,25000000,45,16,4096,0,8192,12,Success,Save to reliable storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>RDD-027,Sample_Fraction,sample,Transformation,rdd.sample(False,0.1,42),10000000,1000000,8,4,1024,0,1024,3,Success,Random sample of data</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>RDD-028,Foreach_Action,foreach,Action,rdd.foreach(print),5000000,0,15,8,512,0,1024,4,Success,Apply function to each element</t>
+        </is>
+      </c>
+      <c r="B29" s="0" t="inlineStr">
+        <is>
+          <t>Coding</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>RDD-029,Save_Text_File,saveAsTextFile,Action,rdd.saveAsTextFile("output/"),15000000,15000000,52,8,2048,0,3072,4,Success,Save RDD to text files</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>RDD-030,Zip_RDDs,zip,Transformation,rdd1.zip(rdd2),5000000,5000000,15,4,1024,0,2048,4,Success,Combine two RDDs element-wise</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="0" t="inlineStr">
+        <is>
+          <t>Question No.</t>
+        </is>
+      </c>
+      <c r="B1" s="0" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C1" s="0" t="inlineStr">
+        <is>
+          <t>Question Type</t>
+        </is>
+      </c>
+      <c r="D1" s="0" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="E1" s="0" t="inlineStr">
+        <is>
+          <t>Scenario/Context</t>
+        </is>
+      </c>
+      <c r="F1" s="0" t="inlineStr">
+        <is>
+          <t>Skills Tested</t>
+        </is>
+      </c>
+      <c r="G1" s="0" t="inlineStr">
+        <is>
+          <t>Option A</t>
+        </is>
+      </c>
+      <c r="H1" s="0" t="inlineStr">
+        <is>
+          <t>Option B</t>
+        </is>
+      </c>
+      <c r="I1" s="0" t="inlineStr">
+        <is>
+          <t>Option C</t>
+        </is>
+      </c>
+      <c r="J1" s="0" t="inlineStr">
+        <is>
+          <t>Option D</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="B2" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C2" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D2" s="0" t="inlineStr">
+        <is>
+          <t>How do you create RDDs in PySpark? List different ways from the dataset with code examples.</t>
+        </is>
+      </c>
+      <c r="E2" s="0" t="inlineStr">
+        <is>
+          <t>Analyze Create operations | textFile: sc.textFile('data.txt'), parallelize: sc.parallelize([1,2,3]), wholeTextFiles: sc.wholeTextFiles('folder/')</t>
+        </is>
+      </c>
+      <c r="F2" s="0" t="inlineStr">
+        <is>
+          <t>RDDs can be created from external data or existing collections</t>
+        </is>
+      </c>
+      <c r="G2" s="0" t="inlineStr"/>
+      <c r="H2" s="0" t="inlineStr"/>
+      <c r="I2" s="0" t="inlineStr"/>
+      <c r="J2" s="0" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
+      <c r="B3" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C3" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D3" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to load a text file and count the number of lines. Use the dataset example.</t>
+        </is>
+      </c>
+      <c r="E3" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-001 and RDD-011 | rdd = sc.textFile('data.txt'); count = rdd.count() -&gt; 10,000,000 lines</t>
+        </is>
+      </c>
+      <c r="F3" s="0" t="inlineStr">
+        <is>
+          <t>textFile loads data; count returns number of elements</t>
+        </is>
+      </c>
+      <c r="G3" s="0" t="inlineStr"/>
+      <c r="H3" s="0" t="inlineStr"/>
+      <c r="I3" s="0" t="inlineStr"/>
+      <c r="J3" s="0" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="0" t="n">
         <v>3</v>
       </c>
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D4" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to filter numbers greater than 100 from an RDD.</t>
+        </is>
+      </c>
+      <c r="E4" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-004 | filtered_rdd = rdd.filter(lambda x: x &gt; 100); result = filtered_rdd.count()</t>
+        </is>
+      </c>
+      <c r="F4" s="0" t="inlineStr">
+        <is>
+          <t>filter applies predicate function; returns new RDD</t>
+        </is>
+      </c>
+      <c r="G4" s="0" t="inlineStr"/>
+      <c r="H4" s="0" t="inlineStr"/>
+      <c r="I4" s="0" t="inlineStr"/>
+      <c r="J4" s="0" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="0" t="n">
         <v>4</v>
       </c>
+      <c r="B5" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C5" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D5" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to apply a function to each element using map. Provide example.</t>
+        </is>
+      </c>
+      <c r="E5" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-005 | mapped_rdd = rdd.map(lambda x: x * 2); result = mapped_rdd.take(5)</t>
+        </is>
+      </c>
+      <c r="F5" s="0" t="inlineStr">
+        <is>
+          <t>map applies function 1:1; transformation is lazy</t>
+        </is>
+      </c>
+      <c r="G5" s="0" t="inlineStr"/>
+      <c r="H5" s="0" t="inlineStr"/>
+      <c r="I5" s="0" t="inlineStr"/>
+      <c r="J5" s="0" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="0" t="n">
         <v>5</v>
       </c>
+      <c r="B6" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C6" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D6" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to split lines into words using flatMap.</t>
+        </is>
+      </c>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-006 | words_rdd = lines_rdd.flatMap(lambda line: line.split()); word_count = words_rdd.count()</t>
+        </is>
+      </c>
+      <c r="F6" s="0" t="inlineStr">
+        <is>
+          <t>flatMap flattens results; useful for 1-to-many transformations</t>
+        </is>
+      </c>
+      <c r="G6" s="0" t="inlineStr"/>
+      <c r="H6" s="0" t="inlineStr"/>
+      <c r="I6" s="0" t="inlineStr"/>
+      <c r="J6" s="0" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="0" t="n">
         <v>6</v>
       </c>
+      <c r="B7" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to sum all numbers in an RDD using reduce.</t>
+        </is>
+      </c>
+      <c r="E7" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-008 | total = numbers_rdd.reduce(lambda a,b: a+b) -&gt; returns aggregated value</t>
+        </is>
+      </c>
+      <c r="F7" s="0" t="inlineStr">
+        <is>
+          <t>reduce aggregates all elements; action triggers computation</t>
+        </is>
+      </c>
+      <c r="G7" s="0" t="inlineStr"/>
+      <c r="H7" s="0" t="inlineStr"/>
+      <c r="I7" s="0" t="inlineStr"/>
+      <c r="J7" s="0" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D8" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to get the first 100 elements from an RDD using take.</t>
+        </is>
+      </c>
+      <c r="E8" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-010 | first_100 = rdd.take(100) -&gt; returns list of 100 elements</t>
+        </is>
+      </c>
+      <c r="F8" s="0" t="inlineStr">
+        <is>
+          <t>take retrieves first n elements; useful for sampling</t>
+        </is>
+      </c>
+      <c r="G8" s="0" t="inlineStr"/>
+      <c r="H8" s="0" t="inlineStr"/>
+      <c r="I8" s="0" t="inlineStr"/>
+      <c r="J8" s="0" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to count frequency of values using countByValue.</t>
+        </is>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-012 | freq = rdd.countByValue() -&gt; returns dict of value-&gt;count</t>
+        </is>
+      </c>
+      <c r="F9" s="0" t="inlineStr">
+        <is>
+          <t>countByValue returns dictionary; action collects results</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr"/>
+      <c r="H9" s="0" t="inlineStr"/>
+      <c r="I9" s="0" t="inlineStr"/>
+      <c r="J9" s="0" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="0" t="n">
         <v>9</v>
       </c>
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to group values by key using groupByKey.</t>
+        </is>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-013 | grouped = rdd.groupByKey(); result = grouped.mapValues(list).take(5)</t>
+        </is>
+      </c>
+      <c r="F10" s="0" t="inlineStr">
+        <is>
+          <t>groupByKey groups all values for each key; wide transformation</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr"/>
+      <c r="H10" s="0" t="inlineStr"/>
+      <c r="I10" s="0" t="inlineStr"/>
+      <c r="J10" s="0" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="0" t="n">
         <v>10</v>
       </c>
+      <c r="B11" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C11" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D11" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to aggregate values by key using reduceByKey.</t>
+        </is>
+      </c>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-014 | sum_by_key = rdd.reduceByKey(lambda a,b: a+b); result = sum_by_key.collect()</t>
+        </is>
+      </c>
+      <c r="F11" s="0" t="inlineStr">
+        <is>
+          <t>reduceByKey performs map-side aggregation; more efficient than groupByKey</t>
+        </is>
+      </c>
+      <c r="G11" s="0" t="inlineStr"/>
+      <c r="H11" s="0" t="inlineStr"/>
+      <c r="I11" s="0" t="inlineStr"/>
+      <c r="J11" s="0" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="0" t="n">
         <v>11</v>
       </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D12" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to sort an RDD by keys using sortByKey.</t>
+        </is>
+      </c>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-015 | sorted_rdd = rdd.sortByKey(); result = sorted_rdd.take(10)</t>
+        </is>
+      </c>
+      <c r="F12" s="0" t="inlineStr">
+        <is>
+          <t>sortByKey sorts by key; requires shuffle</t>
+        </is>
+      </c>
+      <c r="G12" s="0" t="inlineStr"/>
+      <c r="H12" s="0" t="inlineStr"/>
+      <c r="I12" s="0" t="inlineStr"/>
+      <c r="J12" s="0" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="0" t="n">
         <v>12</v>
       </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to perform an inner join between two RDDs.</t>
+        </is>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-016 | joined = rdd1.join(rdd2); result = joined.take(10)</t>
+        </is>
+      </c>
+      <c r="F13" s="0" t="inlineStr">
+        <is>
+          <t>join combines RDDs by key; wide transformation</t>
+        </is>
+      </c>
+      <c r="G13" s="0" t="inlineStr"/>
+      <c r="H13" s="0" t="inlineStr"/>
+      <c r="I13" s="0" t="inlineStr"/>
+      <c r="J13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="0" t="n">
         <v>13</v>
       </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D14" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to combine two RDDs using union.</t>
+        </is>
+      </c>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-017 | combined = rdd1.union(rdd2); result = combined.count()</t>
+        </is>
+      </c>
+      <c r="F14" s="0" t="inlineStr">
+        <is>
+          <t>union combines RDDs; no shuffle required</t>
+        </is>
+      </c>
+      <c r="G14" s="0" t="inlineStr"/>
+      <c r="H14" s="0" t="inlineStr"/>
+      <c r="I14" s="0" t="inlineStr"/>
+      <c r="J14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="0" t="n">
         <v>14</v>
       </c>
+      <c r="B15" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to remove duplicates from an RDD using distinct.</t>
+        </is>
+      </c>
+      <c r="E15" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-018 | unique = rdd.distinct(); count = unique.count()</t>
+        </is>
+      </c>
+      <c r="F15" s="0" t="inlineStr">
+        <is>
+          <t>distinct removes duplicates; requires shuffle</t>
+        </is>
+      </c>
+      <c r="G15" s="0" t="inlineStr"/>
+      <c r="H15" s="0" t="inlineStr"/>
+      <c r="I15" s="0" t="inlineStr"/>
+      <c r="J15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="0" t="n">
         <v>15</v>
       </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C16" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D16" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to find common elements between two RDDs using intersection.</t>
+        </is>
+      </c>
+      <c r="E16" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-019 | common = rdd1.intersection(rdd2); result = common.collect()</t>
+        </is>
+      </c>
+      <c r="F16" s="0" t="inlineStr">
+        <is>
+          <t>intersection finds common elements; requires shuffle</t>
+        </is>
+      </c>
+      <c r="G16" s="0" t="inlineStr"/>
+      <c r="H16" s="0" t="inlineStr"/>
+      <c r="I16" s="0" t="inlineStr"/>
+      <c r="J16" s="0" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="0" t="n">
         <v>16</v>
       </c>
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D17" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to reduce partitions using coalesce.</t>
+        </is>
+      </c>
+      <c r="E17" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-021 | coalesced = rdd.coalesce(4); partitions = coalesced.getNumPartitions()</t>
+        </is>
+      </c>
+      <c r="F17" s="0" t="inlineStr">
+        <is>
+          <t>coalesce reduces partitions without shuffle; efficient</t>
+        </is>
+      </c>
+      <c r="G17" s="0" t="inlineStr"/>
+      <c r="H17" s="0" t="inlineStr"/>
+      <c r="I17" s="0" t="inlineStr"/>
+      <c r="J17" s="0" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="0" t="n">
         <v>17</v>
       </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C18" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D18" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to increase partitions using repartition.</t>
+        </is>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-022 | repartitioned = rdd.repartition(16); partitions = repartitioned.getNumPartitions()</t>
+        </is>
+      </c>
+      <c r="F18" s="0" t="inlineStr">
+        <is>
+          <t>repartition changes partitions with shuffle; use for increasing</t>
+        </is>
+      </c>
+      <c r="G18" s="0" t="inlineStr"/>
+      <c r="H18" s="0" t="inlineStr"/>
+      <c r="I18" s="0" t="inlineStr"/>
+      <c r="J18" s="0" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="0" t="n">
         <v>18</v>
       </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to cache an RDD in memory for reuse.</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-023 | rdd.cache(); result = rdd.count() (first action caches); rdd.unpersist()</t>
+        </is>
+      </c>
+      <c r="F19" s="0" t="inlineStr">
+        <is>
+          <t>cache stores RDD in memory; improves iterative operations</t>
+        </is>
+      </c>
+      <c r="G19" s="0" t="inlineStr"/>
+      <c r="H19" s="0" t="inlineStr"/>
+      <c r="I19" s="0" t="inlineStr"/>
+      <c r="J19" s="0" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="0" t="n">
         <v>19</v>
       </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C20" s="0" t="inlineStr">
+        <is>
+          <t>Theory</t>
+        </is>
+      </c>
+      <c r="D20" s="0" t="inlineStr">
+        <is>
+          <t>Write PySpark code to save an RDD to text files.</t>
+        </is>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>From RDD-029 | rdd.saveAsTextFile('output/') -&gt; creates part-00000, part-00001, etc.</t>
+        </is>
+      </c>
+      <c r="F20" s="0" t="inlineStr">
+        <is>
+          <t>saveAsTextFile writes each partition to separate file</t>
+        </is>
+      </c>
+      <c r="G20" s="0" t="inlineStr"/>
+      <c r="H20" s="0" t="inlineStr"/>
+      <c r="I20" s="0" t="inlineStr"/>
+      <c r="J20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="inlineStr">
+        <is>
+          <t>Working with RDDs in PySpark</t>
+        </is>
+      </c>
+      <c r="C21" s="0" t="inlineStr">
+        <is>
+          <t>Practical</t>
+        </is>
+      </c>
+      <c r="D21" s="0" t="inlineStr">
+        <is>
+          <t>Create a complete PySpark word count example using RDDs.</t>
+        </is>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
+        <is>
+          <t>Combine operations | lines = sc.textFile('file.txt'); words = lines.flatMap(lambda l: l.split()); word_counts = words.map(lambda w: (w,1)).reduceByKey(lambda a,b: a+b); word_counts.saveAsTextFile('output/')</t>
+        </is>
+      </c>
+      <c r="F21" s="0" t="inlineStr">
+        <is>
+          <t>Word count demonstrates RDD transformations and actions</t>
+        </is>
+      </c>
+      <c r="G21" s="0" t="inlineStr"/>
+      <c r="H21" s="0" t="inlineStr"/>
+      <c r="I21" s="0" t="inlineStr"/>
+      <c r="J21" s="0" t="inlineStr"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>